--- a/_doc/AppMsgBox.xlsx
+++ b/_doc/AppMsgBox.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6_YMGLib5\FujisawaIshikai\FMKyuyo\_doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86C4606-1DA2-46DA-A346-834EEAFF4513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A681B0-3ED9-44AD-AEA5-7B53C3906EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26595" yWindow="1905" windowWidth="26130" windowHeight="19890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1140" windowWidth="28800" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="84">
   <si>
     <t>Icon</t>
     <phoneticPr fontId="1"/>
@@ -551,14 +551,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>YesNo</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Question</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>MaxCodeForMaster</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -591,234 +583,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>確認</t>
-    <rPh sb="0" eb="2">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CreateNextMonth</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SuccessNextMonth</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0}月度への更新処理が完了しました。</t>
-    <rPh sb="3" eb="5">
-      <t>ゲツド</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>カンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SelectedMonth</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>処理月度「{0}」が選択されました。</t>
-    <rPh sb="0" eb="2">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ガツ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ConfirmSaveCalendar</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0}分のカレンダー情報を登録します。よろしいですか？</t>
-    <rPh sb="3" eb="4">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>NotFoundCalendarNeedCreate</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>警告</t>
-    <rPh sb="0" eb="2">
-      <t>ケイコク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0}分のカレンダー情報が登録されていません。\r\nカレンダー管理画面で設定情報を登録してください。</t>
-    <rPh sb="3" eb="4">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ConfirmChangePassword</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>パスワードを変更します。よろしいですか？</t>
-    <rPh sb="6" eb="8">
-      <t>ヘンコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ConfirmRemakeKyuyoData</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CreateKyuyoData</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0}度の給与計算データを生成しました。</t>
-    <rPh sb="3" eb="4">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キュウヨ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ケイサン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>セイセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0}度の給与計算データは既に作成済みです。再作成してもよろしいですか？\r\n（該当月度の作成済みデータについては全て破棄されます。）</t>
-    <rPh sb="3" eb="4">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キュウヨ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ケイサン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="22" eb="25">
-      <t>サイサクセイ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ガイトウ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>ガツ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>スベ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>ハキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ClearKyuyoData</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ConfirmClearKyuyoData</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>確定状態を解除するため、作成済みの給与計算データが全てクリアされます。よろしいですか？</t>
-    <rPh sb="0" eb="2">
-      <t>カクテイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カイジョ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>キュウヨ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ケイサン</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>スベ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>@c(Red)解除すると元には戻せません。本当によろしいですか？</t>
-    <rPh sb="7" eb="9">
-      <t>カイジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>@c(Red)削除すると元には戻せません。本当によろしいですか？</t>
     <rPh sb="7" eb="9">
       <t>サクジョ</t>
@@ -835,416 +599,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ConfirmClearKyuyoData2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ConfirmCreateKyuyoData</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0}度の給与計算データをクリアしました。</t>
-    <rPh sb="3" eb="4">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キュウヨ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ケイサン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0}度の給与計算データを作成します。よろしいですか？</t>
-    <rPh sb="3" eb="4">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キュウヨ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ケイサン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SuccessExportLog</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ログファイルの出力が完了しました。</t>
-    <rPh sb="7" eb="9">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ログファイルの出力に失敗しました。ファイルがなんらかのアプリケーションによって開かれている可能性があります。</t>
-    <rPh sb="7" eb="9">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="45" eb="48">
-      <t>カノウセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FailedExportLogReasonSave</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ShutDown</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アプリケーションを終了します。よろしいですか？</t>
-    <rPh sb="9" eb="11">
-      <t>シュウリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>StartRemoteSupport</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>サポートセンターのオペレータによる遠隔支援サービスを開始します。よろしいですか？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Button2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>{0}を削除しますか？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FixedKyuyo</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>給与データが確定済のため、情報を編集する事ができません。</t>
-    <rPh sb="0" eb="2">
-      <t>キュウヨ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カクテイ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>コト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>警告</t>
-    <rPh sb="0" eb="2">
-      <t>ケイコク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0}は現在ログイン中のため、削除することができません。</t>
-    <rPh sb="4" eb="6">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>チュウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CannotDeleteLoginUser</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ConfirmRecalcKyushin</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SuccessRecalcKyushin</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0}件のデータについて、再計算を実行しました。</t>
-    <rPh sb="3" eb="4">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>サイケイサン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>@c(Red)再計算すると元には戻せません。本当によろしいですか？</t>
-    <rPh sb="7" eb="10">
-      <t>サイケイサン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ConfirmRecalcKyushin2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0}の休日診療データについて、現在の日区分と計算区分を元に再計算します。\r\n既に登録されている金額については全て破棄されます。よろしいですか？</t>
-    <rPh sb="4" eb="8">
-      <t>キュウジツシンリョウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>クブン</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ケイサン</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>クブン</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="30" eb="33">
-      <t>サイケイサン</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>スデ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>キンガク</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>スベ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ハキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「{0}度」への更新処理を実行します。よろしいですか？</t>
-    <rPh sb="4" eb="5">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CannotCancelFixedKyuyo</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>過去分（最新月度でない）で確定済みの給与計算データを解除する事はできません。</t>
-    <rPh sb="0" eb="2">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>サイシン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ガツ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カクテイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>キュウヨ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ケイサン</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>カイジョ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>コト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SuccessImportCSV</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CSVファイルから{0}件のデータインポートが完了しました。</t>
-    <rPh sb="12" eb="13">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>カンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CancelImportCSV</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ExecImportCSV</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CSVインポートをキャンセルします。よろしいですか？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CSVファイルからデータのインポートを実行します。よろしいですか？</t>
-    <rPh sb="19" eb="21">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ConfirmIlligalMyNumber</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入力された個人番号は有効ではありません。\r\nこのまま登録してもよろしいですか？</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>コジン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ユウコウ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ログイン中の担当者にマイナンバーを管理する権限がありません。</t>
-    <rPh sb="4" eb="5">
-      <t>チュウ</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ケンゲン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DisabledMyNumber</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マイナンバー管理者のパスワードが登録されていません。\r\nつづけて管理用パスワードを登録してください。</t>
-    <rPh sb="6" eb="8">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>シャ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="34" eb="37">
-      <t>カンリヨウ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MyNumberManagerPWD</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HavenotAuthAdmin</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>指定した機能を実行するには、管理者権限が必要です。</t>
-    <rPh sb="0" eb="2">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="14" eb="17">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ケンゲン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ConfirmImportDuplicate</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>同一月度・診療所にインポート済のデータがあります。インポート処理を実行しますか？</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1678,7 +1033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F218"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="38.875" style="2" bestFit="1" customWidth="1"/>
@@ -1809,7 +1164,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>3</v>
@@ -1849,7 +1204,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>3</v>
@@ -2266,10 +1621,10 @@
     </row>
     <row r="30" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>29</v>
@@ -2285,604 +1640,244 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A31" s="4"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A33" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A32" s="4"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="4"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
     </row>
     <row r="34" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A34" s="4"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A35" s="4"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
     </row>
     <row r="36" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A36" s="4"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
     </row>
     <row r="37" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A37" s="4"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
     </row>
     <row r="38" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A38" s="4"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
     </row>
     <row r="39" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A39" s="4"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
     </row>
     <row r="40" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
     </row>
     <row r="41" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A41" s="4"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
     </row>
     <row r="42" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A42" s="4"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
     </row>
     <row r="43" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A43" s="4"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
     </row>
     <row r="44" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A44" s="4"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
     </row>
     <row r="45" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A45" s="4"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
     </row>
     <row r="46" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A47" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A48" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A46" s="4"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="4"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="4"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
     </row>
     <row r="49" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>118</v>
-      </c>
+      <c r="A49" s="4"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
     </row>
     <row r="50" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>118</v>
-      </c>
+      <c r="A50" s="4"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
     </row>
     <row r="51" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A51" s="4"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
     </row>
     <row r="52" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A52" s="4"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
     </row>
     <row r="53" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A53" s="4"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
     </row>
     <row r="54" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>118</v>
-      </c>
+      <c r="A54" s="4"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
     </row>
     <row r="55" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>118</v>
-      </c>
+      <c r="A55" s="4"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
     </row>
     <row r="56" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>118</v>
-      </c>
+      <c r="A56" s="4"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
     </row>
     <row r="57" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A57" s="4"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
     </row>
     <row r="58" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A58" s="4"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
     </row>
     <row r="59" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A59" s="4"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
     </row>
     <row r="60" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>118</v>
-      </c>
+      <c r="A60" s="4"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
     </row>
     <row r="61" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="4"/>
@@ -3006,7 +2001,7 @@
     </row>
     <row r="76" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="4"/>
-      <c r="B76" s="9"/>
+      <c r="B76" s="12"/>
       <c r="C76" s="7"/>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -3060,7 +2055,7 @@
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="4"/>
       <c r="B83" s="9"/>
       <c r="C83" s="7"/>
@@ -3246,7 +2241,7 @@
     </row>
     <row r="106" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="4"/>
-      <c r="B106" s="12"/>
+      <c r="B106" s="9"/>
       <c r="C106" s="7"/>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
@@ -3300,7 +2295,7 @@
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="4"/>
       <c r="B113" s="9"/>
       <c r="C113" s="7"/>
@@ -3907,246 +2902,6 @@
       <c r="D188" s="6"/>
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
-    </row>
-    <row r="189" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A189" s="4"/>
-      <c r="B189" s="9"/>
-      <c r="C189" s="7"/>
-      <c r="D189" s="6"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
-    </row>
-    <row r="190" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A190" s="4"/>
-      <c r="B190" s="9"/>
-      <c r="C190" s="7"/>
-      <c r="D190" s="6"/>
-      <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
-    </row>
-    <row r="191" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A191" s="4"/>
-      <c r="B191" s="9"/>
-      <c r="C191" s="7"/>
-      <c r="D191" s="6"/>
-      <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
-    </row>
-    <row r="192" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A192" s="4"/>
-      <c r="B192" s="9"/>
-      <c r="C192" s="7"/>
-      <c r="D192" s="6"/>
-      <c r="E192" s="6"/>
-      <c r="F192" s="6"/>
-    </row>
-    <row r="193" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A193" s="4"/>
-      <c r="B193" s="9"/>
-      <c r="C193" s="7"/>
-      <c r="D193" s="6"/>
-      <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
-    </row>
-    <row r="194" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A194" s="4"/>
-      <c r="B194" s="9"/>
-      <c r="C194" s="7"/>
-      <c r="D194" s="6"/>
-      <c r="E194" s="6"/>
-      <c r="F194" s="6"/>
-    </row>
-    <row r="195" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A195" s="4"/>
-      <c r="B195" s="9"/>
-      <c r="C195" s="7"/>
-      <c r="D195" s="6"/>
-      <c r="E195" s="6"/>
-      <c r="F195" s="6"/>
-    </row>
-    <row r="196" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A196" s="4"/>
-      <c r="B196" s="9"/>
-      <c r="C196" s="7"/>
-      <c r="D196" s="6"/>
-      <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
-    </row>
-    <row r="197" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A197" s="4"/>
-      <c r="B197" s="9"/>
-      <c r="C197" s="7"/>
-      <c r="D197" s="6"/>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
-    </row>
-    <row r="198" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A198" s="4"/>
-      <c r="B198" s="9"/>
-      <c r="C198" s="7"/>
-      <c r="D198" s="6"/>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
-    </row>
-    <row r="199" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A199" s="4"/>
-      <c r="B199" s="9"/>
-      <c r="C199" s="7"/>
-      <c r="D199" s="6"/>
-      <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
-    </row>
-    <row r="200" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A200" s="4"/>
-      <c r="B200" s="9"/>
-      <c r="C200" s="7"/>
-      <c r="D200" s="6"/>
-      <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
-    </row>
-    <row r="201" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A201" s="4"/>
-      <c r="B201" s="9"/>
-      <c r="C201" s="7"/>
-      <c r="D201" s="6"/>
-      <c r="E201" s="6"/>
-      <c r="F201" s="6"/>
-    </row>
-    <row r="202" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A202" s="4"/>
-      <c r="B202" s="9"/>
-      <c r="C202" s="7"/>
-      <c r="D202" s="6"/>
-      <c r="E202" s="6"/>
-      <c r="F202" s="6"/>
-    </row>
-    <row r="203" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A203" s="4"/>
-      <c r="B203" s="9"/>
-      <c r="C203" s="7"/>
-      <c r="D203" s="6"/>
-      <c r="E203" s="6"/>
-      <c r="F203" s="6"/>
-    </row>
-    <row r="204" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A204" s="4"/>
-      <c r="B204" s="9"/>
-      <c r="C204" s="7"/>
-      <c r="D204" s="6"/>
-      <c r="E204" s="6"/>
-      <c r="F204" s="6"/>
-    </row>
-    <row r="205" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A205" s="4"/>
-      <c r="B205" s="9"/>
-      <c r="C205" s="7"/>
-      <c r="D205" s="6"/>
-      <c r="E205" s="6"/>
-      <c r="F205" s="6"/>
-    </row>
-    <row r="206" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A206" s="4"/>
-      <c r="B206" s="9"/>
-      <c r="C206" s="7"/>
-      <c r="D206" s="6"/>
-      <c r="E206" s="6"/>
-      <c r="F206" s="6"/>
-    </row>
-    <row r="207" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A207" s="4"/>
-      <c r="B207" s="9"/>
-      <c r="C207" s="7"/>
-      <c r="D207" s="6"/>
-      <c r="E207" s="6"/>
-      <c r="F207" s="6"/>
-    </row>
-    <row r="208" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A208" s="4"/>
-      <c r="B208" s="9"/>
-      <c r="C208" s="7"/>
-      <c r="D208" s="6"/>
-      <c r="E208" s="6"/>
-      <c r="F208" s="6"/>
-    </row>
-    <row r="209" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A209" s="4"/>
-      <c r="B209" s="9"/>
-      <c r="C209" s="7"/>
-      <c r="D209" s="6"/>
-      <c r="E209" s="6"/>
-      <c r="F209" s="6"/>
-    </row>
-    <row r="210" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A210" s="4"/>
-      <c r="B210" s="9"/>
-      <c r="C210" s="7"/>
-      <c r="D210" s="6"/>
-      <c r="E210" s="6"/>
-      <c r="F210" s="6"/>
-    </row>
-    <row r="211" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A211" s="4"/>
-      <c r="B211" s="9"/>
-      <c r="C211" s="7"/>
-      <c r="D211" s="6"/>
-      <c r="E211" s="6"/>
-      <c r="F211" s="6"/>
-    </row>
-    <row r="212" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A212" s="4"/>
-      <c r="B212" s="9"/>
-      <c r="C212" s="7"/>
-      <c r="D212" s="6"/>
-      <c r="E212" s="6"/>
-      <c r="F212" s="6"/>
-    </row>
-    <row r="213" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A213" s="4"/>
-      <c r="B213" s="9"/>
-      <c r="C213" s="7"/>
-      <c r="D213" s="6"/>
-      <c r="E213" s="6"/>
-      <c r="F213" s="6"/>
-    </row>
-    <row r="214" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A214" s="4"/>
-      <c r="B214" s="9"/>
-      <c r="C214" s="7"/>
-      <c r="D214" s="6"/>
-      <c r="E214" s="6"/>
-      <c r="F214" s="6"/>
-    </row>
-    <row r="215" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A215" s="4"/>
-      <c r="B215" s="9"/>
-      <c r="C215" s="7"/>
-      <c r="D215" s="6"/>
-      <c r="E215" s="6"/>
-      <c r="F215" s="6"/>
-    </row>
-    <row r="216" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A216" s="4"/>
-      <c r="B216" s="9"/>
-      <c r="C216" s="7"/>
-      <c r="D216" s="6"/>
-      <c r="E216" s="6"/>
-      <c r="F216" s="6"/>
-    </row>
-    <row r="217" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A217" s="4"/>
-      <c r="B217" s="9"/>
-      <c r="C217" s="7"/>
-      <c r="D217" s="6"/>
-      <c r="E217" s="6"/>
-      <c r="F217" s="6"/>
-    </row>
-    <row r="218" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A218" s="4"/>
-      <c r="B218" s="9"/>
-      <c r="C218" s="7"/>
-      <c r="D218" s="6"/>
-      <c r="E218" s="6"/>
-      <c r="F218" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
